--- a/MedicalBioStatistics/data/D’Agostino-Pearson Omnibus Test.xlsx
+++ b/MedicalBioStatistics/data/D’Agostino-Pearson Omnibus Test.xlsx
@@ -1,14 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12525"/>
+    <workbookView windowWidth="22192" windowHeight="10455"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DAgost" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="DataRange">#REF!</definedName>
+    <definedName name="DataRange2">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -26,31 +30,126 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_2AF9D522D18144299F13E6B999797886"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20883245" y="703580"/>
+          <a:ext cx="15992475" cy="4733925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_8588EA139AA94064B0AEFC691509512A"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14262735" y="329565"/>
+          <a:ext cx="4577080" cy="1727835"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_3C2D6C6629E54EF8900E2EF1004C86ED"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8692515" y="711200"/>
+          <a:ext cx="3637915" cy="1368425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
-  <si>
-    <t>ctrl</t>
-  </si>
-  <si>
-    <t>trt</t>
-  </si>
-  <si>
-    <t>偏度检验</t>
-  </si>
-  <si>
-    <t>峰度检验</t>
-  </si>
-  <si>
-    <t>D’Agostino-Pearson Omnibus Test</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+  <si>
+    <t>https://real-statistics.com/tests-normality-and-symmetry/statistical-tests-normality-symmetry/dagostino-pearson-test/</t>
+  </si>
+  <si>
+    <t>D'Agostino-Pearson Test (sample)</t>
+  </si>
+  <si>
+    <t>Frequency Table</t>
+  </si>
+  <si>
+    <t>Skewness Test</t>
+  </si>
+  <si>
+    <t>Kurtosis Test</t>
+  </si>
+  <si>
+    <t>D'Agostino-Pearson Test</t>
+  </si>
+  <si>
+    <t>Bin size</t>
   </si>
   <si>
     <t>size</t>
   </si>
   <si>
-    <t>statistic</t>
-  </si>
-  <si>
-    <t>=G15^2+K15^2</t>
+    <t>stat</t>
   </si>
   <si>
     <t>alpha</t>
@@ -59,28 +158,61 @@
     <t>p-value</t>
   </si>
   <si>
-    <t>=CHIDIST(O11,2)</t>
-  </si>
-  <si>
-    <t>skew</t>
+    <t>=CHISQ.DIST.RT(AB5,2)</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>freq</t>
+  </si>
+  <si>
+    <t>cum</t>
+  </si>
+  <si>
+    <t>skewness</t>
   </si>
   <si>
     <t>kurtosis</t>
   </si>
   <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>Z_s statistic</t>
-  </si>
-  <si>
-    <t>Z_k statistic</t>
+    <t>Shapiro-Wilk Test</t>
+  </si>
+  <si>
+    <t>s.e.</t>
+  </si>
+  <si>
+    <t>test stat：Zs=skew/s.e.</t>
+  </si>
+  <si>
+    <t>test stat：Zk=kurt/s.e</t>
+  </si>
+  <si>
+    <t>=2*NORM.S.DIST(-ABS(R10),TRUE)</t>
+  </si>
+  <si>
+    <t>=2*NORM.S.DIST(-ABS(W10),TRUE)</t>
   </si>
   <si>
     <t>lower</t>
   </si>
   <si>
+    <t>=R8-R9*NORM.S.INV(1-R6/2)</t>
+  </si>
+  <si>
+    <t>=W8-W9*NORM.S.INV(1-W6/2)</t>
+  </si>
+  <si>
     <t>upper</t>
+  </si>
+  <si>
+    <t>=R8+R9*NORM.S.INV(1-R6/2)</t>
+  </si>
+  <si>
+    <t>=W8+W9*NORM.S.INV(1-W6/2)</t>
+  </si>
+  <si>
+    <t>test stat</t>
   </si>
 </sst>
 </file>
@@ -93,33 +225,11 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -127,22 +237,30 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -150,7 +268,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -158,7 +276,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -166,7 +284,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -174,7 +292,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -182,14 +300,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -197,7 +315,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -205,7 +323,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -213,14 +331,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -228,42 +346,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -468,12 +586,120 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="19">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -577,19 +803,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -598,143 +833,148 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -788,13 +1028,323 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Histogram</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>DAgost!$E$11:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DAgost!$F$11:$F$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="777235192"/>
+        <c:axId val="777232840"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="777235192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Bin</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="777232840"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="777232840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Frequency</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="777235192"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{b747933d-9367-4b62-9938-47c656a1beb2}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304165</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>55245</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>647065</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3834765" y="582930"/>
+        <a:ext cx="3571875" cy="2209800"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -808,44 +1358,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -872,14 +1422,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -906,6 +1457,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -917,599 +1469,933 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AD32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="1" max="2" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
-    <col min="7" max="8" width="13.75" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
-    <col min="11" max="12" width="13.75" customWidth="1"/>
-    <col min="15" max="15" width="29.5" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
+    <col min="1" max="1" width="3.20353982300885" customWidth="1"/>
+    <col min="2" max="3" width="5" customWidth="1"/>
+    <col min="13" max="13" width="9.20353982300885" customWidth="1"/>
+    <col min="15" max="15" width="13.2743362831858"/>
+    <col min="17" max="17" width="11.8672566371681" customWidth="1"/>
+    <col min="18" max="18" width="13.2743362831858"/>
+    <col min="19" max="19" width="3.73451327433628" customWidth="1"/>
+    <col min="20" max="20" width="39.7345132743363" customWidth="1"/>
+    <col min="21" max="21" width="13.2743362831858"/>
+    <col min="22" max="22" width="10.2300884955752" customWidth="1"/>
+    <col min="23" max="23" width="13.858407079646"/>
+    <col min="24" max="24" width="3.73451327433628" customWidth="1"/>
+    <col min="25" max="25" width="51.5309734513274" customWidth="1"/>
+    <col min="27" max="28" width="13.2743362831858"/>
+    <col min="29" max="29" width="3.73451327433628" customWidth="1"/>
+    <col min="30" max="30" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="3" spans="1:30">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
+    <row r="5" ht="28.3" spans="1:30">
+      <c r="E5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" t="str">
+        <f>_xlfn.DISPIMG("ID_3C2D6C6629E54EF8900E2EF1004C86ED",1)</f>
+        <v>=DISPIMG("ID_3C2D6C6629E54EF8900E2EF1004C86ED",1)</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="W5" t="str">
+        <f>_xlfn.DISPIMG("ID_8588EA139AA94064B0AEFC691509512A",1)</f>
+        <v>=DISPIMG("ID_8588EA139AA94064B0AEFC691509512A",1)</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB5" t="str">
+        <f>_xlfn.DISPIMG("ID_2AF9D522D18144299F13E6B999797886",1)</f>
+        <v>=DISPIMG("ID_2AF9D522D18144299F13E6B999797886",1)</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
+      <c r="B6" s="5">
         <v>34</v>
       </c>
-      <c r="B2">
+      <c r="C6" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
+    <row r="7" spans="1:30">
+      <c r="B7" s="7">
         <v>56</v>
       </c>
-      <c r="B3">
+      <c r="C7" s="8">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="9">
+        <f>COUNT(B6:C17)</f>
+        <v>24</v>
+      </c>
+      <c r="T7" t="e">
+        <f>FTEXT(R7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="V7" t="s">
+        <v>7</v>
+      </c>
+      <c r="W7" s="9">
+        <f>COUNT(B6:C17)</f>
+        <v>24</v>
+      </c>
+      <c r="Y7" t="e">
+        <f>FTEXT(W7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB7" s="10">
+        <f>R12^2+W12^2</f>
+        <v>0.90425586277437</v>
+      </c>
+      <c r="AD7" t="e">
+        <f>FTEXT(AB7)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
+      <c r="B8" s="7">
         <v>39</v>
       </c>
-      <c r="B4">
+      <c r="C8" s="8">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
+      <c r="Q8" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="V8" t="s">
+        <v>9</v>
+      </c>
+      <c r="W8" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="11">
+        <f>CHIDIST(AB7,2)</f>
+        <v>0.636272765260617</v>
+      </c>
+      <c r="AD8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
+      <c r="B9" s="7">
         <v>71</v>
       </c>
-      <c r="B5">
+      <c r="C9" s="8">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
+      <c r="E9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
+      <c r="B10" s="7">
         <v>84</v>
       </c>
-      <c r="B6">
+      <c r="C10" s="8">
         <v>88</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
+      <c r="E10">
+        <f>E11-$F$7</f>
+        <v>14</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>15</v>
+      </c>
+      <c r="R10" s="10">
+        <f>SKEW(B6:C17)</f>
+        <v>0.195700749750972</v>
+      </c>
+      <c r="T10" t="e">
+        <f>FTEXT(R10)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="V10" t="s">
+        <v>16</v>
+      </c>
+      <c r="W10" s="10">
+        <f>KURT(B6:C17)</f>
+        <v>-0.785509837227702</v>
+      </c>
+      <c r="Y10" t="e">
+        <f>FTEXT(W10)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
+      <c r="B11" s="7">
         <v>92</v>
       </c>
-      <c r="B7">
+      <c r="C11" s="8">
         <v>53</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
+      <c r="E11">
+        <f t="shared" ref="E11:E16" si="0">E12-$F$7</f>
+        <v>26</v>
+      </c>
+      <c r="F11">
+        <f>G11-G10</f>
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <f t="shared" ref="G11:G17" si="1">COUNTIF($B$6:$C$17,"&lt;="&amp;E11)</f>
+        <v>1</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" s="13">
+        <f>SQRT(6*R7*(R7-1)/((R7-2)*(R7+1)*(R7+3)))</f>
+        <v>0.472260842152198</v>
+      </c>
+      <c r="T11" t="e">
+        <f>FTEXT(R11)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="V11" t="s">
+        <v>18</v>
+      </c>
+      <c r="W11" s="13">
+        <f>2*(W7-1)*SQRT(6*W7/((W7-2)*(W7-3)*(W7+3)*(W7+5)))</f>
+        <v>0.917777082601901</v>
+      </c>
+      <c r="Y11" t="e">
+        <f>FTEXT(W11)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="12" ht="27.75" spans="1:30">
+      <c r="B12" s="7">
         <v>44</v>
       </c>
-      <c r="B8">
+      <c r="C12" s="8">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ref="F12:F17" si="2">G12-G11</f>
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="R12" s="13">
+        <f>R10/R11</f>
+        <v>0.414391226804069</v>
+      </c>
+      <c r="T12" t="e">
+        <f>FTEXT(R12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="V12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="W12" s="13">
+        <f>W10/W11</f>
+        <v>-0.855883037524514</v>
+      </c>
+      <c r="Y12" t="e">
+        <f>FTEXT(W12)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB12" s="10"/>
+      <c r="AD12" t="e">
+        <f>FTEXT(AB12)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
+      <c r="B13" s="7">
         <v>67</v>
       </c>
-      <c r="B9">
+      <c r="C13" s="8">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10">
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>10</v>
+      </c>
+      <c r="R13" s="13">
+        <f>2*NORMSDIST(-ABS(R12))</f>
+        <v>0.678587612976682</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="V13" t="s">
+        <v>10</v>
+      </c>
+      <c r="W13" s="13">
+        <f>2*NORMSDIST(-ABS(W12))</f>
+        <v>0.392062478323808</v>
+      </c>
+      <c r="Y13" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB13" s="11" t="e">
+        <f>SWTEST(B6:C17)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD13" t="e">
+        <f>FTEXT(AB13)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
+      <c r="B14" s="7">
         <v>98</v>
       </c>
-      <c r="B10">
+      <c r="C14" s="8">
         <v>36</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="J10" s="2" t="s">
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>23</v>
+      </c>
+      <c r="R14" s="13">
+        <f>R10-R11*NORMSINV(1-R8/2)</f>
+        <v>-0.729913492175891</v>
+      </c>
+      <c r="T14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" t="s">
+        <v>23</v>
+      </c>
+      <c r="W14" s="13">
+        <f>W10-W11*NORMSINV(1-W8/2)</f>
+        <v>-2.58431986496367</v>
+      </c>
+      <c r="Y14" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
+      <c r="B15" s="7">
+        <v>49</v>
+      </c>
+      <c r="C15" s="8">
+        <v>66</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>26</v>
+      </c>
+      <c r="R15" s="11">
+        <f>R10+R11*NORMSINV(1-R8/2)</f>
+        <v>1.12131499167783</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="V15" t="s">
+        <v>26</v>
+      </c>
+      <c r="W15" s="11">
+        <f>W10+W11*NORMSINV(1-W8/2)</f>
+        <v>1.01330019050827</v>
+      </c>
+      <c r="Y15" s="18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
+      <c r="B16" s="7">
+        <v>55</v>
+      </c>
+      <c r="C16" s="8">
+        <v>77</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="N10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11">
-        <v>49</v>
-      </c>
-      <c r="B11">
-        <v>66</v>
-      </c>
-      <c r="F11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <f>COUNT(A24:A39)</f>
-        <v>16</v>
-      </c>
-      <c r="J11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K11">
-        <f>COUNT(A24:A39)</f>
-        <v>16</v>
-      </c>
-      <c r="N11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O11">
-        <f>G15^2+K15^2</f>
-        <v>0.638870353324863</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12">
-        <v>55</v>
-      </c>
-      <c r="B12">
-        <v>77</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30">
+      <c r="B17" s="15">
+        <v>73</v>
+      </c>
+      <c r="C17" s="16">
+        <v>35</v>
+      </c>
+      <c r="E17" s="17">
+        <f>MAX(B6:C17)</f>
+        <v>98</v>
+      </c>
+      <c r="F17" s="17">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G17" s="17">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:30">
+      <c r="E20" t="e">
+        <f>FTEXT(E22)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="H20" t="e">
+        <f>FTEXT(H22)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Q20" t="e">
+        <f t="array" ref="Q20:R25">SKEWTEST(B6:C17,TRUE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="R20" s="10" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="T20" t="e">
+        <f>FTEXT(Q20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="V20" t="e">
+        <f t="array" ref="V20:W25">KURTTEST(B6:C17,TRUE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="W20" s="10" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="Y20" t="e">
+        <f>FTEXT(V20)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA20" t="s">
         <v>8</v>
       </c>
-      <c r="G12">
-        <v>0.05</v>
-      </c>
-      <c r="J12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12">
-        <v>0.05</v>
-      </c>
-      <c r="N12" t="s">
-        <v>9</v>
-      </c>
-      <c r="O12">
-        <f>CHIDIST(O11,2)</f>
-        <v>0.726559298848188</v>
-      </c>
-      <c r="P12" s="6" t="s">
+      <c r="AB20" s="10" t="e">
+        <f>DAGOSTINO(B6:C17,FALSE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD20" t="e">
+        <f>FTEXT(AB20)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="21" spans="2:30">
+      <c r="Q21" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="R21" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="V21" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="W21" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="AA21" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>73</v>
-      </c>
-      <c r="B13">
-        <v>35</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <f>SKEW(A2:B13)</f>
-        <v>0.195700749750972</v>
-      </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13">
-        <f>KURT(A2:B13)</f>
-        <v>-0.785509837227702</v>
-      </c>
-    </row>
-    <row r="14" spans="6:14">
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <f>SQRT(6*G11*(G11-1)/((G11-2)*(G11+1)*(G11+3)))</f>
-        <v>0.564307688003965</v>
-      </c>
-      <c r="J14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14">
-        <f>2*(K11-1)*SQRT(6*K11/((K11-2)*(K11-3)*(K11+3)*(K11+5)))</f>
-        <v>1.09077387938705</v>
-      </c>
-      <c r="N14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="6:14">
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="4">
-        <f>G13/G14</f>
-        <v>0.34679795067686</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="4">
-        <f>K13/K14</f>
-        <v>-0.720139941074784</v>
-      </c>
-      <c r="N15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="6:11">
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <f>1-_xlfn.NORM.S.DIST(ABS(G15),TRUE)</f>
-        <v>0.364371558412104</v>
-      </c>
-      <c r="J16" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16">
-        <f>1-_xlfn.NORM.S.DIST(ABS(K15),TRUE)</f>
-        <v>0.235719418913425</v>
-      </c>
-    </row>
-    <row r="17" spans="6:11">
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <f>G13-G14*_xlfn.NORM.S.INV(1-G12/2)</f>
-        <v>-0.910321994935865</v>
-      </c>
-      <c r="J17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K17">
-        <f>K13-K14*_xlfn.NORM.S.INV(1-K12/2)</f>
-        <v>-2.92338735610335</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18">
-        <f>SKEW(A2:A13)</f>
-        <v>0.268981667584299</v>
-      </c>
-      <c r="B18">
-        <f>SKEW(B2:B13)</f>
-        <v>0.0191305619881483</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18">
-        <f>G13+G14*_xlfn.NORM.S.INV(1-G12/2)</f>
-        <v>1.30172349443781</v>
-      </c>
-      <c r="J18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18">
-        <f>K13+K14*_xlfn.NORM.S.INV(1-K12/2)</f>
-        <v>1.35236768164795</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>2</v>
-      </c>
-      <c r="B24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>6</v>
-      </c>
-      <c r="B25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>13</v>
-      </c>
-      <c r="B26">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>5</v>
-      </c>
-      <c r="B27">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
-        <v>8</v>
-      </c>
-      <c r="B28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>9</v>
-      </c>
-      <c r="B29">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>12</v>
-      </c>
-      <c r="B30">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
-        <v>11</v>
-      </c>
-      <c r="B31">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>8</v>
-      </c>
-      <c r="B32">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
+      <c r="AB21" s="11" t="e">
+        <f>DPTEST(B6:C17,FALSE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AD21" t="e">
+        <f>FTEXT(AB21)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="22" spans="2:30">
+      <c r="E22" t="e">
+        <f t="array" ref="E22:F26">SKEWTEST(B6:C17,TRUE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F22" s="10" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H22" t="e">
+        <f t="array" ref="H22:I26">KURTTEST(B6:C17,TRUE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I22" s="10" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="K22" t="s">
+        <v>29</v>
+      </c>
+      <c r="L22" s="10" t="e">
+        <f>DAGOSTINO(B6:C17,FALSE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="M22" t="e">
+        <f>FTEXT(L22)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Q22" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="R22" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="V22" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="W22" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="23" spans="2:30">
+      <c r="E23" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="F23" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="I23" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="K23" t="s">
         <v>10</v>
       </c>
-      <c r="B33">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>12</v>
-      </c>
-      <c r="B34">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>14</v>
-      </c>
-      <c r="B35">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>13</v>
-      </c>
-      <c r="B36">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>6</v>
-      </c>
-      <c r="B37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>7</v>
-      </c>
-      <c r="B38">
+      <c r="L23" s="11" t="e">
+        <f>DPTEST(B6:C17,FALSE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="M23" t="e">
+        <f>FTEXT(L23)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Q23" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="R23" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="V23" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="W23" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="24" spans="2:30">
+      <c r="E24" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="F24" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="I24" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="Q24" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="R24" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="V24" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="W24" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="25" spans="2:30">
+      <c r="E25" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="F25" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="I25" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="K25" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" s="10" t="e">
+        <f>DAGOSTINO(B6:C17)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="M25" t="e">
+        <f>FTEXT(L25)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Q25" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="R25" s="11" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="V25" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="W25" s="11" t="e">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="26" spans="2:30">
+      <c r="E26" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="F26" s="11" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="I26" s="11" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="K26" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>4</v>
-      </c>
-      <c r="B39">
-        <v>10</v>
+      <c r="L26" s="11" t="e">
+        <f>DPTEST(B6:C17)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="M26" t="e">
+        <f>FTEXT(L26)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="28" spans="2:30">
+      <c r="E28" t="e">
+        <f>FTEXT(E30)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="H28" t="e">
+        <f>FTEXT(H30)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="30" spans="2:30">
+      <c r="E30" t="e">
+        <f t="array" ref="E30:F32">SKEWPTEST(B6:C17,TRUE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F30" s="10" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H30" t="e">
+        <f t="array" ref="H30:I32">KURTPTEST(B6:C17,TRUE)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I30" s="10" t="e">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="31" spans="2:30">
+      <c r="E31" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="F31" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H31" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="I31" s="13" t="e">
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="32" spans="2:30">
+      <c r="E32" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="F32" s="11" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="H32" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="I32" s="11" t="e">
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="N10:O10"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId2" display="https://real-statistics.com/tests-normality-and-symmetry/statistical-tests-normality-symmetry/dagostino-pearson-test/"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>